--- a/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
+++ b/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
@@ -1157,7 +1157,7 @@
   &gt;
 .
 [20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 292 個 CEID(與貴端現場機台的字典逐筆相同，含本機已註冊但不發射的 236 個)〔20260803:由 275 補齊為 292〕；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。
-[20260805] ⚠ 補充兩點對位與上限說明：(1) 與 S1F4 / S2F14 不同，S1F24 每一筆都帶 CEID，貴端可直接以 CEID 對號取值，不需依請求順序對位；&lt;L[0]&gt; 全查的回覆順序為 CEID 號碼遞增。(2) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機字典目前 292 筆，故全查不會觸及此上限，但貴端若以 S2F35 連結了本機未註冊的 CEID，該號碼會被建立進字典、筆數隨之增加，請留意。</t>
+[20260805] ⚠ 補充兩點對位與上限說明：(1) 與 S1F4 / S2F14 不同，S1F24 每一筆都帶 CEID，貴端可直接以 CEID 對號取值，不需依請求順序對位；&lt;L[0]&gt; 全查的回覆順序為 CEID 號碼遞增。(2) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機字典目前 292 筆，故全查不會觸及此上限，但貴端若以 S2F35 連結了本機未註冊的 CEID，該號碼會被建立進字典、筆數隨之增加，請留意。(3) ⚠ 每一個 CEID 的 VID 清單上限為 1024 個 —— 本機內建報表遠低於此，但貴端若以 S2F33 定義了超大報表並連結到同一個 CEID，超出的 VID 會被靜默截斷(機台端只寫一行 log)，此時該筆的 VID 清單會短於實際連結內容。</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,8 @@
     &gt;
   &gt;
 .
-[20260804] 已實作。可寫的 EC 只有兩組：ECID 1007 Operator ID(不受 idle 閘，運轉中亦可寫)與 2758-2763 Tray 幾何(僅機台閒置且機內無 IC 時受理)。〔20260805 更正：原文「其餘號碼一律不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)」與「忙碌閘排在號碼判定之前 …… 閒下來再送只會由 2 改成 1」兩段敘述有誤，已刪除並改寫為下列四點。⚠ 貴端若曾依原敘述設計重試邏輯(收到 2 就等閒置重送、收到 1 才視為永久失敗)，請一併檢查 —— 本機的方向正好相反。〕(1) 號碼白名單先判：本機不可寫或未登錄的號碼(含已登錄但唯讀的 1501，以及 1006、37007、16000、16002、16023、16026、35011 等未登錄號碼)恆回 EAC=1，與機台是否運轉無關 —— 機台閒下來再送仍然是 1，不會變成 2，也永遠不會成功。(2) EAC=2 只在「整包號碼全部可寫、且其中含 tray 幾何 2758-2763 而機台忙碌(運轉中或機內尚有 IC)」時才會出現。例如忙碌時送 {1007 ＋ 任一 tray 幾何}：1007 這一筆通過、tray 幾何這一筆得 2，整包仍回 2(整包不寫入)。(3) 多筆失敗時只回報最嚴重的一個，優先序為 1 &gt; 3 &gt; 2 —— 1=本機永遠不會接受、3=號碼可寫但值不合格、2=號碼與值都沒問題，機台閒置後重送即可。(4) EAC 值域：0=整包受理並寫入 / 1=封包格式錯誤，或含本機不可寫、未登錄的號碼 / 2=機台忙碌(只可能由 tray 幾何 2758-2763 引起) / 3=值無法轉為數值(tray 幾何)或 ECID 1007 送空字串。
+[20260804] 已實作。可寫的 EC 只有兩組：ECID 1007 Operator ID(不受 idle 閘，運轉中亦可寫)與 2758-2763 Tray 幾何(僅機台閒置且機內無 IC 時受理)。〔20260805 更正：原文「其餘號碼一律不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)」與「忙碌閘排在號碼判定之前 …… 閒下來再送只會由 2 改成 1」兩段敘述有誤，已刪除並改寫為下列四點。⚠ 貴端若曾依原敘述設計重試邏輯(收到 2 就等閒置重送、收到 1 才視為永久失敗)，請一併檢查 —— 本機的方向正好相反。〕(1) 號碼白名單先判：本機不可寫或未登錄的號碼(含已登錄但唯讀的 1501，以及 1006、37007、16000、16002、16023、16026、35011 等未登錄號碼)恆回 EAC=1，與機台是否運轉無關 —— 機台閒下來再送仍然是 1，不會變成 2，也永遠不會成功。(2) EAC=2 只在「整包號碼全部可寫、且其中含 tray 幾何 2758-2763 而機台忙碌(運轉中或機內尚有 IC)」時才會出現。例如忙碌時送 {1007 ＋ 任一 tray 幾何}：1007 這一筆通過、tray 幾何這一筆得 2，整包仍回 2(整包不寫入)。(3) 多筆失敗時只回報最嚴重的一個，優先序為 1 &gt; 3 &gt; 2 —— 1=本機永遠不會接受、3=號碼可寫但值不合格、2=號碼與值都沒問題，機台閒置後重送即可。(5) ⚠ 單一 S2F15 封包最多 32 個項目(ECID/ECV 對)。超過的部分一律回 EAC=1，而 EAC 非 0 時整包不寫入 —— 也就是超過 32 筆會導致整包被拒。請貴端拆包送出。
+(4) EAC 值域：0=整包受理並寫入 / 1=封包格式錯誤，或含本機不可寫、未登錄的號碼 / 2=機台忙碌(只可能由 tray 幾何 2758-2763 引起) / 3=值無法轉為數值(tray 幾何)或 ECID 1007 送空字串。
 ⚠ 混合封包請拆開送(2026-08-04 實測)。S2F16 的 EAC 是「整包一個值」，而本機是逐筆套用。以貴端 2026-06-08 對 HT-9046 送的同一種封包 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 實測本機：1007 的值確實已寫入並存檔(可由 S2F13 讀回)，但整包回 EAC=1、且不發 CEID 48 —— 「部分成功卻回報失敗」。HT-9046 不會如此(它的忙碌閘是整包擋在寫入之前)。依程式碼判讀，同一現象在機台忙碌時亦會發生(此時整包回 EAC=2，1007 仍已寫入 —— 因為 1007 的處理排在忙碌閘之前)；⚠ 此忙碌情形尚未實測，2026-08-04 的實測全部在機台閒置下進行(實得 EAC 僅 0 / 1 / 3)，本方將於上機驗證時補齊。貴端當天另有一筆是把 1007 與 37007 包在一起，37007 本機同樣未登錄，故該形狀也會踩到同一個現象。〔20260804 追加項：本缺陷已修復並實測通過 —— S2F15 改為「先整包檢查、全部可寫且不忙碌才逐筆套用」，混合封包現在一律整包拒絕、完全不寫入、也不發 CEID 48(實測 {1006,1007} 回 EAC=1 且 Operator ID 維持原值)。同時 ECV 的型別解析已補齊(F8 / F4 / BOOLEAN 現在都讀得出來)，且無法轉為數值的 tray 值一律回 EAC=3 不寫入，不再出現「靜默寫 0」。因此下列兩條送包規則對修正後的韌體已非必要；若貴端機台尚未更新韌體，請仍照下列規則送〕在舊版韌體上，⚠ 請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成為一個封包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一個封包，不得混入本機不可寫或未登錄的號碼(1501、1006、37007、16000、16002、16023、16026、35011 等)，並僅在機台閒置且機內無 IC 時送出。⚠ 特別提醒(以下三種情形皆為舊版韌體行為)：「整包都是可寫的號碼」並不等於安全 —— 因為 1007 排在忙碌閘之前，運轉中送 {1007＋任一 tray 幾何} 時，1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2 且不發事件；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進當前配方檔(存檔只看該筆是否寫成功，不看 EAC)。原則：一個封包只放一個號碼最安全，最低限度是 1007 絕不與其他號碼同包。不含 1007 的純 tray 幾何封包是全有全無(忙碌時整包拒絕、閒置時整包寫入並發 CEID 48)，可安全合併。以上三種情形在 2026-08-04 之後的韌體上都不會發生 —— 一律整包拒絕、完全不寫入。
 ⚠ 另請注意：S2F30 回報的 ECMIN / ECMAX 目前是零長度(未宣告，與 HT9045 相同)，寫入路徑也不做數值範圍檢查；tray 幾何若無法解出數值就會被當 0 寫入並存進配方檔。〔20260804 追加項：已修 —— 現在 ASCII 與 F8 / F4 / BOOLEAN、U1-U4 / I1-I4 都可作為 ECV 送出，本機依收到的型別解出數值；無法轉為數值者(例如 ASCII 'abc'、空 item)一律回 EAC=3 且不寫入，不會再出現「回 EAC=0 卻寫進 0」。舊版韌體則會 —— 若貴端機台尚未更新，請一律以 ASCII 送 ECV。實測：&lt;F8 71.5&gt; 寫 2760 得 EAC=0 且值為 71.5；ASCII 'abc' 得 EAC=3 且值不變。詳見「ECID」工作表第 (5) 點。〕</t>
         </is>
@@ -4626,21 +4627,21 @@
     <row r="69">
       <c r="A69" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (a)〕AMR 系列 SVID 38199-38245（共 36 個號碼）僅在 system\General.ini [HardwareInstall] UseAMR=1 時維護。UseAMR=0（本機出廠預設，也是一般量產模式）時這些值不再刷新，停留在開機初值（數值為 0、字串為零長度）；S1F3 仍可讀到，但內容沒有意義，請勿據以判斷機台實況。</t>
+          <t>〔20260805 追加項：表尾註 (a)〕AMR 系列 SVID 38199-38245(共 36 個號碼)僅在 system\General.ini [HardwareInstall] UseAMR=1 時維護。UseAMR=0(本機出廠預設，也是一般量產模式)時這些值不再刷新，停留在開機初值(數值為 0、字串為零長度)；S1F3 仍可讀到，但內容沒有意義，請勿據以判斷機台實況。⚠ 一個例外：SVID 38204 Color Carrier ID 的更新路徑(Color CCD 讀到身分盤 2D 時發布)本身不受 UseAMR 影響，因此 UseAMR=0 下只要走到身分盤讀碼流程，38204 仍會被更新並送出 CEID 275。其餘 35 個號碼確實只在 UseAMR=1 時維護。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (b)〕⚠ SVID 38202 Loader Carrier ID 已註冊，但本機從不寫入，恆回零長度字串。身分盤的 2D 由 Color CCD 讀取，並發布在 SVID 38204 Color Carrier ID（CEID 275 內建的 Report 7 也只含 38204）。請貴端把自訂報表 RPTID 2000 內的 38202 換成 38204，否則該格永遠是空的。</t>
+          <t>〔20260805 追加項：表尾註 (b)〕⚠ SVID 38202 Loader Carrier ID 已註冊，但本機從不寫入，恆回零長度字串。身分盤的 2D 由 Color CCD 讀取，並發布在 SVID 38204 Color Carrier ID(CEID 275 內建的 Report 7 也只含 38204)。請貴端把自訂報表 RPTID 2000 內的 38202 換成 38204，否則該格永遠是空的。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (c)〕⚠ 下列五個號碼只是為了對齊站別向量而註冊，本機不維護其值，恆為 0 或零長度字串：38203（Empty Carrier ID）、38223／38224（Empty／Color Tray Count）、38229／38230（Empty／Color Device Count）。原因是 Empty 與 Color 兩站完全由 sensor 與 TrayArm 驅動、不經 SECS，機構上也沒有疊盤計數器。CEID 272／274 的 Report 6 內這幾格同樣恆 0，請勿用來判斷實際盤數。</t>
+          <t>〔20260805 追加項：表尾註 (c)〕⚠ 下列五個號碼只是為了對齊站別向量而註冊，本機不維護其值，恆為 0 或零長度字串：38203(Empty Carrier ID)、38223/38224(Empty/Color Tray Count)、38229/38230(Empty/Color Device Count)。原因是 Empty 與 Color 兩站完全由 sensor 與 TrayArm 驅動、不經 SECS，機構上也沒有疊盤計數器。CEID 272/274 的 Report 6 內這幾格同樣恆 0，請勿用來判斷實際盤數。</t>
         </is>
       </c>
     </row>
@@ -10823,8 +10824,8 @@
     <row r="295">
       <c r="A295" s="30" t="inlineStr">
         <is>
-          <t>註(2026-08-04)：第 3 欄「HT-160」標 V = 本機真的會發射；標「—」= 已註冊但無發射點，永不送出。⚠ 標「V(條件：出廠預設關閉)」者目前只有 CEID 78 Jam Skip IC Count：它有發射點，但需在機台 system\General.ini 的 [SECS] 段加入 AskSkipICCount=1 才會送出，而出貨的 General.ini 未含此鍵，等同關閉 —— 未開啟前訂閱此號碼收不到任何事件。開啟後，操作員在警報畫面以 SKIP 解除警報時會被詢問「本盤取出幾顆 IC?」，輸入並確認後韌體才先閂鎖 SVID 37010 再送出本事件；按取消則不送。〔20260805 更正：發射點合計 56 個 = 45 個無條件 + 10 個需 [HardwareInstall] UseAMR=1（35/36/37/148/149/150 Auto Full 與 272/273/274/275 AMR）+ 1 個需 [SECS] AskSkipICCount=1（CEID 78），其餘 236 個永不送出。前版寫成「55 個無條件 + CEID 78 條件發射」是錯的 —— 那 10 個 UseAMR 條件發射的號碼被誤計為無條件。〕
-⚠ [20260805] 上述 10 個 UseAMR 條件號碼請特別注意：35/36/37/148/149/150 的名稱(Auto1-6 Full)看起來像通用生產事件，但它們與 272/273/274/275 一樣，全部只在 system\General.ini 的 [HardwareInstall] UseAMR=1 時才會送出；UseAMR 出廠預設為 false，而 AMR=0 正是一般量產模式。也就是說在不接 AMR 的一般量產下，貴端訂閱這 10 個號碼永遠收不到事件，請勿以「沒收到 Auto Full」推論車未滿。第 3 欄已就這 10 列改標「V（條件：UseAMR=1）」。
+          <t>註(2026-08-04)：第 3 欄「HT-160」標 V = 本機真的會發射；標「—」= 已註冊但無發射點，永不送出。⚠ 標「V(條件：AskSkipICCount=1)」者目前只有 CEID 78 Jam Skip IC Count：它有發射點，但需在機台 system\General.ini 的 [SECS] 段加入 AskSkipICCount=1 才會送出，而出貨的 General.ini 未含此鍵，等同關閉 —— 未開啟前訂閱此號碼收不到任何事件。開啟後，操作員在警報畫面以 SKIP 解除警報時會被詢問「本盤取出幾顆 IC?」，輸入並確認後韌體才先閂鎖 SVID 37010 再送出本事件；按取消則不送。〔20260805 更正：發射點合計 56 個 = 45 個無條件 + 10 個需 [HardwareInstall] UseAMR=1(35/36/37/148/149/150 Auto Full 與 272/273/274/275 AMR)+ 1 個需 [SECS] AskSkipICCount=1(CEID 78)，其餘 236 個永不送出。前版寫成「55 個無條件 + CEID 78 條件發射」是錯的 —— 那 10 個 UseAMR 條件發射的號碼被誤計為無條件。〕
+⚠ [20260805] 上述 10 個 UseAMR 條件號碼請特別注意：35/36/37/148/149/150 的名稱(Auto1-6 Full)看起來像通用生產事件，但它們與 272/273/274/275 一樣，全部只在 system\General.ini 的 [HardwareInstall] UseAMR=1 時才會送出；UseAMR 出廠預設為 false，而 AMR=0 正是一般量產模式。也就是說在不接 AMR 的一般量產下，貴端訂閱這 10 個號碼永遠收不到事件，請勿以「沒收到 Auto Full」推論車未滿。第 3 欄已就這 10 列改標「V(條件：UseAMR=1)」。
 [20260805] 第 2 欄「事件名稱」為便於閱讀已拆出前置編號；S1F24 回的 CENAME 實際字串為「&lt;CEID&gt; &lt;事件名稱&gt;」(例：CEID 1 回 '1 Start Pressed')，與貴端 EventReport_CEID.def 的 Alias 欄完全相同。貴端若要以字串比對，請以「&lt;CEID&gt; + 一個半角空白 + 事件名稱」組出比對字串，勿直接取用本欄文字。另 CEID 74/75/79 的 CENAME 為非空的 '74'、'75'、'79 '(79 末尾含一個半角空白)，只有 CEID 142/143/144 才是真正的零長度空字串。
 [20260805] 第 4 欄「Report」= 韌體預設把該 CEID 掛在哪張報表；第 5 欄「備註」= 發射條件與發射點說明。這兩欄在前一版客戶版被整欄裁掉，本版還原。⚠ 貴端以 S2F33/S2F35 自訂的連結會取代第 4 欄所列的預設報表，且該連結為 session-only(每次復電後退回韌體預設)，請於復電程序重新送出 S2F33 + S2F35。
 ⚠ [20260805] 本表 292 筆的號碼與名稱與貴端現場機台的 EventReport_CEID.def 逐筆相同。此承諾在本日之前有一個例外：前版韌體在處理 S2F35 事件-報表連結時會把被連結 CEID 的別名清成空字串，之後 S1F23/S1F24 回的該筆 CENAME 就變成零長度(復電後才恢復)。該缺陷已於 2026-08-05 修正 —— 現在只有帶入非空別名時才會更新別名，單純建立連結不再影響別名，因此「逐筆相同」在整個連線期間都成立。</t>

--- a/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
+++ b/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>[20260729] HT-160S 為 Tray Sorter，無測試機構，故無測試結果。分選結果以 SVID 1102 Output Total Count、各 Bin 分選數與 Production log / Soter CSV 提供。〔20260804 第 6 版更正：原寫 SVID 66021 Total Sorted，該號碼已下架；1102 綁的是同一個計數器(值完全相同)，請改讀 1102。〕
+          <t>[20260729] HT-160S 為 Tray Sorter，無測試機構，故無測試結果。分選結果以 SVID 1102 Output Total Count、各 Bin 分選數與 Production log / Soter CSV 提供。〔20260805:1102 的語意已改為「吸嘴確實把 IC 放進 Auto 出料盤」才 +1(對齊 HT9045 / HT-172)，先前只計 2D 反查命中的顆數。詳見「SVID」工作表 1102 一列與本表「輸出計數對帳說明」一列。〕〔20260804 第 6 版更正：原寫 SVID 66021 Total Sorted，該號碼已下架；1102 綁的是同一個計數器(值完全相同)，請改讀 1102。〕
 〔20260805 更正：原文末句「詳見第 31 項」所指的段落只存在於本方內部維護用的「修訂說明」工作表，客戶版不含該頁，故就地敘述 —— 66021 Total Sorted 與 1102 Output Total Count 自始綁同一個計數器，值完全相同，下架 66021 屬純去重、無資訊損失；66021 自 20260804 起為永久空號、本方永不挪用，舊設定若仍綁 66021，S1F3 與報表該格回零長度 list item &lt;L[0]&gt;，list 長度不變、後續欄位不位移。66xxx 十個號碼的完整下架清單與各自替代號碼，請見本表「資料收集 #1 機台狀態變化回報」一格。另請一併參閱本表「輸出計數對帳說明」一列 —— 1102 有其歸零時點(epoch)與對帳限制。〕</t>
         </is>
       </c>
@@ -1909,7 +1909,10 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>[20260729] RCMD CLEAN_OUT(2026-07-29 新增，對齊 HT9045)。僅能自 Normal 運轉模式進入，非 Normal 回 HCACK=2；排空後送 CEID 42 Clean Out Finish 再自動 Lot End。</t>
+          <t>[20260729] RCMD CLEAN_OUT(2026-07-29 新增，對齊 HT9045)。僅能自 Normal 運轉模式進入，非 Normal 回 HCACK=2;排空後送 CEID 42 Clean Out Finish。
+[20260805] ⚠ 兩點請務必納入貴端流程設計(經 2026-08-05 裁定，維持現行韌體行為、於本文件揭露):
+(1) ⚠ 排空完成後的自動 Lot End **只在 AMR 模式(General.ini [HardwareInstall] UseAMR=1)下發生**。非 AMR 模式(UseAMR=0，本機出廠預設，也是一般量產模式)下，排空完成只送 CEID 42 Clean Out Finish，接著由機台跳出提示等操作員確認，**不會**自動結批、**不會**送出 CEID 8 Lot End。貴端收到 CEID 42 後請勿等待結批事件 —— 非 AMR 模式下該事件不會來，結批需由操作員在機台上完成，或由貴端另行送出 RCMD CLEAR_LOT_INFO。(本欄原寫「排空後送 CEID 42 再自動 Lot End」未區分模式，特此更正。)
+(2) ⚠ 對**停止中**的機台送 CLEAN_OUT 仍會回 HCACK=0 並武裝排料模式。此時機台不會立刻開始排空 —— 該狀態會被保留到操作員下一次按 Start，屆時機台會直接進入排料模式；若當下機內已無 IC，排空條件立即成立，操作員會看到「按了 Start 卻馬上跳出 Clean Out 完成並停機」。建議貴端只在機台運轉中送出本命令。</t>
         </is>
       </c>
     </row>
@@ -2469,9 +2472,13 @@
 • 1102 Output Total Count 是 RAM 值，不做斷電保存 —— 復電後回 0。
 • 1101、1103-1105、1259-1261 隨機台的 lastdata 檔保存，復電後還原為斷電前的值。
 • ⚠ 因此復電後、下一次 Lot Start 之前，1102 會明顯小於各站計數(常為 0 對非 0)。這是兩種保存策略的差異，不是掉數，請勿據此判定機台異常或發起重送。
-三、⚠ 明文禁止以「1102 等於各站總和」對帳
-1102 與各站計數是不同的計數器、不同的累加點，本機**不保證** 1102 = 1103 + 1104 + 1105 + 1259 + 1260 + 1261，HT9045 亦不保證(9045 的 1102 是整個 bin 陣列 24 格的總和，不是 RPTID 501 那幾格的總和)。上述第二點的電源循環差異也會讓兩邊在同一時刻對不起來。
-請貴端不要以此等式做完整性檢查或稽核判定。需要逐站對帳請直接把各站計數相加；需要整批對帳請以機台的 Production log 或 Soter 輸出 CSV 為準。
+三、1102 與各站總和的關係
+〔20260805 變更：本段原為「明文禁止以 1102 等於各站總和對帳」。依貴端裁示，1102 的累加點已改到「吸嘴把 IC 放進 Auto 出料盤」的當下(對齊 HT9045 / HT-172)，與各站計數 1103-1105 / 1259-1261 完全同一個事件，因此在同一批內兩者現在確實相等。原禁止條款撤銷，改為下列三個仍會不相等的情形。〕
+⚠ 下列三種情形 1102 仍不等於各站總和，請勿據此判定機台異常：
+• 復電之後、下一次 Lot Start 之前 —— 1102 是 RAM 值回 0，各站計數由 lastdata 還原為斷電前的值(見第二點)。
+• 執行過 S2F41 CLEAN_AUTO_SORT_COUNT 之後 —— 該命令清各站計數但不清 1102，之後 1102 會大於總和。
+• 讀取的瞬間正好落在同一顆 IC 的兩個計數器更新之間(同一事件內相鄰兩行)，可能差 1。
+需要整批對帳請以機台的 Production log 或 Soter 輸出 CSV 為準。需要逐站對帳請直接把各站計數相加；需要整批對帳請以機台的 Production log 或 Soter 輸出 CSV 為準。
 另請注意：貴端 RPTID 501 的第 6 至第 8 格要求的是 SVID 1106-1108(HT9045 的 Fix1-3)，本機未註冊這三個號碼，該三格恆回零長度 list item &lt;L[0]&gt;；HT-160S 的 Auto4-6 在 1259-1261，若貴端要在同一張報表看到六站，請以 S2F33 把 1259-1261 加入報表定義。</t>
         </is>
       </c>
@@ -3038,8 +3045,10 @@
       </c>
       <c r="F16" s="45" t="inlineStr">
         <is>
-          <t>為 RAM 值、復電歸零(不隨 lastdata.dat 保存)，每次 Lot Start 亦歸零。
-⚠ CLEAN_AUTO_SORT_COUNT 不清它 —— 執行該命令後請勿以 1102 對各站計數的總和。</t>
+          <t>[20260805] ⚠ 本號的語意已變更。自本版韌體起，1102 只在「吸嘴確實把 IC 放進 Auto 出料盤」的當下 +1，與 HT9045 / HT-172 一致。
+〔20260805 變更前的行為(供比對舊資料用):累加點埋在 Loader 的 CCD 掃描分支，只有「2D 反查命中」才 +1。因此 2D 讀不到、讀到但不在任何批的 IC 雖然實體照樣被分選進 Error Auto，卻不計入；而未載入 2D 對照表的批次(LotRegistry 為空)更是恆為 0，機台明明在出料。貴端若有本版之前的歷史數據，該數據是「已辨識」而非「已出料」的顆數，兩者不可直接比較。〕
+為 RAM 值、復電歸零(不隨 lastdata.dat 保存)，每次 Lot Start 亦歸零。
+⚠ CLEAN_AUTO_SORT_COUNT 會清各站計數但不清本號，執行該命令後兩者會不一致。</t>
         </is>
       </c>
     </row>
@@ -3649,12 +3658,14 @@
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>恆為零長度字串</t>
+          <t>身分盤的 2D 碼字串；開機後尚未讀到任何身分盤時為零長度</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>⚠ 本號已註冊但本機從不寫入，恆回零長度 —— 身分盤 2D 由 Color CCD 讀取並發布在 SVID 38204(CEID 275 內建的 Report 7 也是 38204)。請貴端把自訂報表 RPTID 2000 內的 38202 換成 38204。詳見表尾註 (b)。</t>
+          <t>[20260805] 身分盤的 2D 由 Color CCD 讀取，讀到有效碼時寫入本 SVID 並發出 CEID 275(其內建 Report 7 僅含本號)。
+〔20260805 變更：本號先前已註冊但從不寫入、恆回零長度，值放在 SVID 38204。依貴端要求「與 HT9045 對齊優先」，韌體已改為發布在本號 —— 貴端自訂報表 RPTID 2000 的第一格(38202 Load port carrier ID)自此會帶到實際值，不需修改貴端設定。⚠ 請注意機構事實與號碼並不一致：實際讀 2D 的是 Color 站的讀碼器，不是 Loader 的 load port;本機以 HT9045 的號碼公布該值，是刻意的對齊決定。〕
+⚠ 讀取失敗或被操作員跳過時會保留上一盤的身分碼(不清空，也不送 CEID 275);讀碼器關閉時產生的佔位字串不會上傳。</t>
         </is>
       </c>
     </row>
@@ -3709,14 +3720,12 @@
       </c>
       <c r="E38" s="40" t="inlineStr">
         <is>
-          <t>身分盤的 2D 碼字串；開機後尚未讀到任何身分盤時為零長度</t>
+          <t>恆為零長度字串</t>
         </is>
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>身分盤 2D 由 Color CCD 讀取，讀到有效碼時寫入本 SVID 並發出 CEID 275(其 Report 7 僅含本號)。
-⚠ 讀取失敗或被操作員跳過時會保留上一盤的身分碼(不清空，也不送 CEID 275)；讀碼器關閉時產生的佔位字串不會上傳。
-本號是 38202 的實際去處，詳見表尾註 (b)。</t>
+          <t>〔20260805 變更：本號自本版起**不再有任何寫入者**，恆回零長度。身分盤 2D 已依貴端要求改發布在 SVID 38202(見該列)。〕本號仍為對齊站別向量而註冊，請勿再用它取身分盤 2D。</t>
         </is>
       </c>
     </row>
@@ -4627,21 +4636,21 @@
     <row r="69">
       <c r="A69" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (a)〕AMR 系列 SVID 38199-38245(共 36 個號碼)僅在 system\General.ini [HardwareInstall] UseAMR=1 時維護。UseAMR=0(本機出廠預設，也是一般量產模式)時這些值不再刷新，停留在開機初值(數值為 0、字串為零長度)；S1F3 仍可讀到，但內容沒有意義，請勿據以判斷機台實況。⚠ 一個例外：SVID 38204 Color Carrier ID 的更新路徑(Color CCD 讀到身分盤 2D 時發布)本身不受 UseAMR 影響，因此 UseAMR=0 下只要走到身分盤讀碼流程，38204 仍會被更新並送出 CEID 275。其餘 35 個號碼確實只在 UseAMR=1 時維護。</t>
+          <t>〔20260805 追加項：表尾註 (a)〕AMR 系列 SVID 38199-38245(共 36 個號碼)僅在 system\General.ini [HardwareInstall] UseAMR=1 時維護。UseAMR=0(本機出廠預設，也是一般量產模式)時這些值不再刷新，停留在開機初值(數值為 0、字串為零長度)；S1F3 仍可讀到，但內容沒有意義，請勿據以判斷機台實況。⚠ 一個例外：SVID 38202 Loader Carrier ID(身分盤 2D)的更新路徑不受 UseAMR 影響，因此 UseAMR=0 下只要走到身分盤讀碼流程，38202 仍會被更新並送出 CEID 275。其餘 35 個號碼確實只在 UseAMR=1 時維護。〔20260805 更正：本句原本指的是 38204；身分盤 2D 已改發布在 38202。〕</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (b)〕⚠ SVID 38202 Loader Carrier ID 已註冊，但本機從不寫入，恆回零長度字串。身分盤的 2D 由 Color CCD 讀取，並發布在 SVID 38204 Color Carrier ID(CEID 275 內建的 Report 7 也只含 38204)。請貴端把自訂報表 RPTID 2000 內的 38202 換成 38204，否則該格永遠是空的。</t>
+          <t>〔20260805 追加項：表尾註 (b)〕⚠ 身分盤 2D 的公布號碼為 SVID 38202 Loader Carrier ID，與 HT9045 一致 —— 貴端自訂報表 RPTID 2000 的第一格不需修改。本版之前該值放在 SVID 38204 Color Carrier ID(因為 Color 站才是實際讀 2D 的讀碼器)，依貴端 2026-08-05 的裁示「與 9045 對齊優先」已改回 38202;CEID 275 內建的 Report 7 亦隨之改為僅含 38202。⚠ 連帶影響：SVID 38204 自此不再有任何寫入者、恆回零長度，請勿再引用。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="43" t="inlineStr">
         <is>
-          <t>〔20260805 追加項：表尾註 (c)〕⚠ 下列五個號碼只是為了對齊站別向量而註冊，本機不維護其值，恆為 0 或零長度字串：38203(Empty Carrier ID)、38223/38224(Empty/Color Tray Count)、38229/38230(Empty/Color Device Count)。原因是 Empty 與 Color 兩站完全由 sensor 與 TrayArm 驅動、不經 SECS，機構上也沒有疊盤計數器。CEID 272/274 的 Report 6 內這幾格同樣恆 0，請勿用來判斷實際盤數。</t>
+          <t>〔20260805 追加項：表尾註 (c)〕⚠ 下列六個號碼只是為了對齊站別向量而註冊，本機不維護其值，恆為 0 或零長度字串：38203(Empty Carrier ID)、38204(Color Carrier ID，自 20260805 起，見表尾註 (b))、38223/38224(Empty/Color Tray Count)、38229/38230(Empty/Color Device Count)。原因是 Empty 與 Color 兩站完全由 sensor 與 TrayArm 驅動、不經 SECS，機構上也沒有疊盤計數器。CEID 272/274 的 Report 6 內這幾格同樣恆 0，請勿用來判斷實際盤數。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
+++ b/docs/SECS/SECS_GEM功能_HandlerV1_20260805.xlsx
@@ -1015,7 +1015,8 @@
  &lt;U4 [1] 1003&gt;
 &gt;
 .
-[20260805] 已實作。S1F3 -&gt; S1F4 回 L,n{SV 值}。⚠ 兩點請注意(與第 8 項 S2F13 / S2F14 同構)：(1) S1F4 的酬載依 SEMI E5 不回 SVID，請以「請求的順序」對位取值；本機未登錄的 SVID 回一個零長度項目(不是錯誤)，故 L 長度恆等於請求筆數、欄位不會位移。(2) 若送 &lt;L[0]&gt; 全查，回覆的 67 個值是本機的註冊順序，不是號碼遞增 —— 本檔「SVID」工作表為便於閱讀採號碼遞增排序，⚠ 請勿用該表的列序對位。實際註冊順序如下，前段 31 個：1001、1003、1021、1027、4、9、3、1002、1009、1006、1007、1008、1011、1101、1102、1103、1104、1105、1259、1260、1261、1517、37010、1518、1501、2758、2759、2760、2761、2762、2763；AMR 段 36 個：38219、38220、38221、38202、38222、38228、38203、38223、38229、38204、38224、38230、38205、38225、38231、38234、38206、38226、38232、38235、38207、38227、38233、38236、38199、38237、38240、38243、38200、38238、38241、38244、38201、38239、38242、38245(每個 Auto 站的 Bin Setting 緊跟在該站的 Carrier / Tray / Device 之後，不是另起一輪)，合計 67 筆。⚠ 建議貴端一律指名 SVID、不要送 &lt;L[0]&gt; —— 註冊順序會隨韌體改版而變動，指名取值才不受影響。⚠ 另請注意：單筆請求的指名清單上限為 512 筆，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)，此時回覆的 L 長度會小於請求筆數；本機只有 67 個 SVID，正常使用不會觸及此上限。</t>
+[20260805] 已實作。S1F3 -&gt; S1F4 回 L,n{SV 值}。⚠ 兩點請注意(與第 8 項 S2F13 / S2F14 同構)：(1) S1F4 的酬載依 SEMI E5 不回 SVID，請以「請求的順序」對位取值；本機未登錄的 SVID 回一個零長度項目(不是錯誤)，故 L 長度恆等於請求筆數、欄位不會位移。(2) 若送 &lt;L[0]&gt; 全查，回覆的 67 個值是本機的註冊順序，不是號碼遞增 —— 本檔「SVID」工作表為便於閱讀採號碼遞增排序，⚠ 請勿用該表的列序對位。實際註冊順序如下，前段 31 個：1001、1003、1021、1027、4、9、3、1002、1009、1006、1007、1008、1011、1101、1102、1103、1104、1105、1259、1260、1261、1517、37010、1518、1501、2758、2759、2760、2761、2762、2763；AMR 段 36 個：38219、38220、38221、38202、38222、38228、38203、38223、38229、38204、38224、38230、38205、38225、38231、38234、38206、38226、38232、38235、38207、38227、38233、38236、38199、38237、38240、38243、38200、38238、38241、38244、38201、38239、38242、38245(每個 Auto 站的 Bin Setting 緊跟在該站的 Carrier / Tray / Device 之後，不是另起一輪)，合計 67 筆。⚠ 建議貴端一律指名 SVID、不要送 &lt;L[0]&gt; —— 註冊順序會隨韌體改版而變動，指名取值才不受影響。⚠ 另請注意：單筆請求的指名清單上限為 512 筆，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)，此時回覆的 L 長度會小於請求筆數；本機只有 67 個 SVID，正常使用不會觸及此上限。
+〔20260805 韌體修正：共用解析器〕先前若請求清單中有一筆是**零長度的非 ASCII 型別**(例如 &lt;F8[0]&gt;)、或本機不支援的型別(U8 / I8 / BINARY)，該筆會卡在解析佇列最前端，導致其後的每一格都重複讀到同一筆壞資料、全部回零長度或 0。現已修正：該筆會被完整跳過，只有那一格回零長度，**其後各格的對位完全不受影響**。⚠ 這也是本表「不回號碼、請以請求順序對位取值」與「L 長度恆等於請求筆數、欄位不會位移」兩項承諾自本版起才**無條件**成立的原因 —— 在此之前，只要請求中夾了一顆本機讀不出的項目，該承諾就會失效。貴端一律以 ASCII 或本表宣告的型別送出號碼，即不會觸發此情形。</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1045,8 @@
   &lt;L [0] 
   &gt;
 .
-[20260805] 已實作。S1F11 -&gt; S1F12 回 L,n{L,3{U4 SVID, A SVNAME, A UNITS}}。⚠ 三點請注意：(1) 與 S1F4 / S2F14 不同，S1F12 每一筆都帶 SVID，貴端可直接以 SVID 對號取值，不需依請求順序對位；本機未登錄的 SVID 回 {SVID, '', ''}(名稱與單位皆為零長度，不是錯誤)。(2) 若送 &lt;L[0]&gt; 全查，回覆的 67 筆順序是本機的註冊順序，不是號碼遞增 —— 本檔「SVID」工作表採號碼遞增排序，⚠ 請勿用它推斷回覆順序；完整註冊順序見第 2 項 S1F3 的說明。(3) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機目前只有 67 個 SVID，故全查不會觸及此上限。</t>
+[20260805] 已實作。S1F11 -&gt; S1F12 回 L,n{L,3{U4 SVID, A SVNAME, A UNITS}}。⚠ 三點請注意：(1) 與 S1F4 / S2F14 不同，S1F12 每一筆都帶 SVID，貴端可直接以 SVID 對號取值，不需依請求順序對位；本機未登錄的 SVID 回 {SVID, '', ''}(名稱與單位皆為零長度，不是錯誤)。(2) 若送 &lt;L[0]&gt; 全查，回覆的 67 筆順序是本機的註冊順序，不是號碼遞增 —— 本檔「SVID」工作表採號碼遞增排序，⚠ 請勿用它推斷回覆順序；完整註冊順序見第 2 項 S1F3 的說明。(3) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機目前只有 67 個 SVID，故全查不會觸及此上限。
+〔20260805 韌體修正：共用解析器〕先前若請求清單中有一筆是**零長度的非 ASCII 型別**(例如 &lt;F8[0]&gt;)、或本機不支援的型別(U8 / I8 / BINARY)，該筆會卡在解析佇列最前端，導致其後的每一格都重複讀到同一筆壞資料、全部回零長度或 0。現已修正：該筆會被完整跳過，只有那一格回零長度，**其後各格的對位完全不受影響**。⚠ 這也是本表「不回號碼、請以請求順序對位取值」與「L 長度恆等於請求筆數、欄位不會位移」兩項承諾自本版起才**無條件**成立的原因 —— 在此之前，只要請求中夾了一顆本機讀不出的項目，該承諾就會失效。貴端一律以 ASCII 或本表宣告的型別送出號碼，即不會觸發此情形。</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1129,9 @@
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>S1F17(On-Line):'S1F17' W
-.</t>
+.
+[20260805] 已實作。S1F17 -&gt; S1F18 ONLACK。⚠ 本機的控制狀態受操作員在機台端的設定節制(SEMI E30)：操作員把機台設為 EQUIPMENT OFF-LINE 時，host 的上線請求會被否決，回 ONLACK=1。
+〔20260805 韌體修正：開機視窗〕機台開機後、控制狀態種子([SECS] InitialControlState)套用前收到的 S1F17，先前會被誤判為 EQUIPMENT OFF-LINE 而回 ONLACK=1;⚠ 若貴端 host 在收到 ONLACK=1 後不重送，機台會整場保持離線。現已修正：S1F18 會先套用種子再判定，出廠組態(InitialControlState=5 On-Line Remote)下該情形改回 ONLACK=2「已在線上」。</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1161,8 @@
   &gt;
 .
 [20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 292 個 CEID(與貴端現場機台的字典逐筆相同，含本機已註冊但不發射的 236 個)〔20260803:由 275 補齊為 292〕；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。
-[20260805] ⚠ 補充兩點對位與上限說明：(1) 與 S1F4 / S2F14 不同，S1F24 每一筆都帶 CEID，貴端可直接以 CEID 對號取值，不需依請求順序對位；&lt;L[0]&gt; 全查的回覆順序為 CEID 號碼遞增。(2) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機字典目前 292 筆，故全查不會觸及此上限，但貴端若以 S2F35 連結了本機未註冊的 CEID，該號碼會被建立進字典、筆數隨之增加，請留意。(3) ⚠ 每一個 CEID 的 VID 清單上限為 1024 個 —— 本機內建報表遠低於此，但貴端若以 S2F33 定義了超大報表並連結到同一個 CEID，超出的 VID 會被靜默截斷(機台端只寫一行 log)，此時該筆的 VID 清單會短於實際連結內容。</t>
+[20260805] ⚠ 補充兩點對位與上限說明：(1) 與 S1F4 / S2F14 不同，S1F24 每一筆都帶 CEID，貴端可直接以 CEID 對號取值，不需依請求順序對位；&lt;L[0]&gt; 全查的回覆順序為 CEID 號碼遞增。(2) 指名清單與 &lt;L[0]&gt; 全查皆受「單筆請求最多 512 筆」的上限，超過的部分會被靜默截斷(S1F3 / S1F11 / S1F23 / S2F13 四支相同)；本機字典目前 292 筆，故全查不會觸及此上限，但貴端若以 S2F35 連結了本機未註冊的 CEID，該號碼會被建立進字典、筆數隨之增加，請留意。(3) ⚠ 每一個 CEID 的 VID 清單上限為 1024 個 —— 本機內建報表遠低於此，但貴端若以 S2F33 定義了超大報表並連結到同一個 CEID，超出的 VID 會被靜默截斷(機台端只寫一行 log)，此時該筆的 VID 清單會短於實際連結內容。
+〔20260805 韌體修正：共用解析器〕先前若請求清單中有一筆是**零長度的非 ASCII 型別**(例如 &lt;F8[0]&gt;)、或本機不支援的型別(U8 / I8 / BINARY)，該筆會卡在解析佇列最前端，導致其後的每一格都重複讀到同一筆壞資料、全部回零長度或 0。現已修正：該筆會被完整跳過，只有那一格回零長度，**其後各格的對位完全不受影響**。⚠ 這也是本表「不回號碼、請以請求順序對位取值」與「L 長度恆等於請求筆數、欄位不會位移」兩項承諾自本版起才**無條件**成立的原因 —— 在此之前，只要請求中夾了一顆本機讀不出的項目，該承諾就會失效。貴端一律以 ASCII 或本表宣告的型別送出號碼，即不會觸發此情形。</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1193,8 @@
   &gt;
 .
 [20260804] 已實作。本機共登錄 8 個 EC(詳見「ECID」工作表)。⚠ 兩點請注意：(1) S2F14 的酬載是 L,n{ECV} —— 依 SEMI E5 不回 ECID，請以「請求的順序」對位取值；(2) 若送 &lt;L[0]&gt; 全查，回覆順序是本機的註冊順序 1501、1007、2760、2758、2761、2759、2762、2763(不是號碼遞增，且 Start / Pitch 是交錯的)。未登錄的 ECID 回一個零長度項目(不是錯誤)，故 L 長度恆等於請求筆數、欄位不會位移。
-[20260805] ⚠ 追加：單筆 S2F13 的指名清單上限為 512 筆，超過的部分會被靜默截斷 —— 此時回覆的 L 長度會小於請求筆數，上面「L 長度恆等於請求筆數」這句在超過 512 筆時不成立。同一上限也適用於 S1F3 / S1F11 / S1F23。本機只有 8 個 EC，正常使用不會觸及。</t>
+[20260805] ⚠ 追加：單筆 S2F13 的指名清單上限為 512 筆，超過的部分會被靜默截斷 —— 此時回覆的 L 長度會小於請求筆數，上面「L 長度恆等於請求筆數」這句在超過 512 筆時不成立。同一上限也適用於 S1F3 / S1F11 / S1F23。本機只有 8 個 EC，正常使用不會觸及。
+〔20260805 韌體修正：共用解析器〕先前若請求清單中有一筆是**零長度的非 ASCII 型別**(例如 &lt;F8[0]&gt;)、或本機不支援的型別(U8 / I8 / BINARY)，該筆會卡在解析佇列最前端，導致其後的每一格都重複讀到同一筆壞資料、全部回零長度或 0。現已修正：該筆會被完整跳過，只有那一格回零長度，**其後各格的對位完全不受影響**。⚠ 這也是本表「不回號碼、請以請求順序對位取值」與「L 長度恆等於請求筆數、欄位不會位移」兩項承諾自本版起才**無條件**成立的原因 —— 在此之前，只要請求中夾了一顆本機讀不出的項目，該承諾就會失效。貴端一律以 ASCII 或本表宣告的型別送出號碼，即不會觸發此情形。</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1260,8 @@
   &gt;
 .
 [20260730] 已實作(2026-07-30 新增)。S2F29 -&gt; S2F30 回 L,n{L,6{U4 ECID, A ECNAME, ECMIN, ECMAX, ECDEF, A ECUNITS}}。&lt;L[0]&gt; 全查回全部 8 個 EC，回覆順序即本機的註冊順序(不是號碼遞增)：1501 Setup File、1007 Operator ID、2760 Type 1 Tray Start Position X、2758 Type 1 Tray Pitch X、2761 Type 1 Tray Start Position Y、2759 Type 1 Tray Pitch Y、2762 Type 1 Tray Division X、2763 Type 1 Tray Division Y〔20260804 追加項：名稱已對齊 HT-90XX，1501 由 Recipe Name 改為 Setup File、2758-2763 由短名改為 Type 1 … 全名，與本機 SV 側及貴端機台完全相同；號碼、型別、單位與值皆未變〕。〔20260804 更正：原文「7 個」是 2026-08-03 新增 ECID 1007 之前的數字；全查的 L 長度已由 7 變 8，請以回覆內的 ECID 對號取值，勿以固定筆數或固定位置解析。〕ECMIN / ECMAX / ECDEF 以該 EC 自身宣告的型別編碼(例如 FT_8 的 Tray X Start 回 FT_8，不是 ASCII)；未宣告上下限者回該型別的零長度項目(E5「未宣告」的表示法，與 HT9045 相同)。未註冊的 ECID 回 L,6 內名稱 / 三個界限 / 單位皆為零長度。註：本訊息為唯讀查詢；EC 寫入仍走 S2F15，維持「只開放 tray 幾何(2758-2763)」與「機台閒置才受理」兩道限制，S2F30 不會放寬可寫範圍。〔20260804 更正：自 2026-08-03 起唯一的例外是 ECID 1007 Operator ID —— 它不是 tray 幾何，且刻意不受 idle 閘、運轉中亦接受寫入(空字串回 EAC=3)。貴端 2026-06-08 現場在運轉當下寫 ECID 1007 = "AGV" 的那幾筆，在本機會被受理，不會被拒。〕
-[20260804] 本機的 EC 目錄已列於本檔新增的「ECID」工作表(第 5 張)，含號碼 / 名稱 / 型別 / 單位 / 可寫性 / 說明，以及貴端 host 曾以 S2F15 寫入但本機未登錄的號碼清單。該表內容係以 headless SECS host 對實際韌體實測 S2F29 &lt;L[0]&gt; 的回覆逐格記錄，非人工整理。</t>
+[20260804] 本機的 EC 目錄已列於本檔新增的「ECID」工作表(第 5 張)，含號碼 / 名稱 / 型別 / 單位 / 可寫性 / 說明，以及貴端 host 曾以 S2F15 寫入但本機未登錄的號碼清單。該表內容係以 headless SECS host 對實際韌體實測 S2F29 &lt;L[0]&gt; 的回覆逐格記錄，非人工整理。
+〔20260805 韌體修正：共用解析器〕先前若請求清單中有一筆是**零長度的非 ASCII 型別**(例如 &lt;F8[0]&gt;)、或本機不支援的型別(U8 / I8 / BINARY)，該筆會卡在解析佇列最前端，導致其後的每一格都重複讀到同一筆壞資料、全部回零長度或 0。現已修正：該筆會被完整跳過，只有那一格回零長度，**其後各格的對位完全不受影響**。⚠ 這也是本表「不回號碼、請以請求順序對位取值」與「L 長度恆等於請求筆數、欄位不會位移」兩項承諾自本版起才**無條件**成立的原因 —— 在此之前，只要請求中夾了一顆本機讀不出的項目，該承諾就會失效。貴端一律以 ASCII 或本表宣告的型別送出號碼，即不會觸發此情形。</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1533,10 @@
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>:'S6F15' W
-&lt;L [2] 
-  &lt;U4 [1] 0&gt;
-  &lt;U4 [1] 1&gt;
-&gt;
+&lt;U4 [1] 1&gt;
 .
-[20260729] 已實作(2026-07-28 新增)。裸 &lt;U4 CEID&gt; 與 L,1 包裝皆接受；未註冊的 CEID 回 L,3{DATAID,CEID,L,0}；解析失敗回 CEID=0，不會不回覆。</t>
+[20260729] 已實作(2026-07-28 新增)。裸 &lt;U4 CEID&gt; 與 L,1 包裝皆接受；未註冊的 CEID 回 L,3{DATAID,CEID,L,0}；解析失敗回 CEID=0，不會不回覆。
+〔20260805 更正：本列原印的範例是 &lt;L[2] &lt;U4 0&gt; &lt;U4 1&gt;&gt;(DATAID + CEID 兩格)，⚠ 本機不接受該形狀 —— 它會剝掉 list 外殼後讀第一格，把 DATAID 的 0 當成 CEID，回 L,3{DATAID,CEID=0,L,0}「無此事件」，而且不會有任何錯誤指示。依 SEMI E5，S6F15 的本體本來就只有 CEID 一格，多出來的那一格是本表的筆誤。貴端現場實際送的是裸 &lt;U4[1] CEID&gt;(3/3 筆)，與更正後的範例一致，故貴端無須調整；若曾有人照舊範例撰寫程式，會出現「永遠拉不到資料卻也沒有錯誤」的症狀，請一併檢查。本機接受的兩種形狀為：裸 &lt;U4 CEID&gt;，以及 &lt;L[1] &lt;U4 CEID&gt;&gt;。〕</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1743,8 @@
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>SVID:1027
-[20260803] 另新增 SVID 3 GemClock(GEM 標準號),同一時刻但採 SEMI E5 16 字元格式'YYYYMMDDhhmmsscc'(與本機 S2F18 回覆同格式)；1027 維持 'yyyy/mm/dd hh:nn:ss'。</t>
+[20260803] 另新增 SVID 3 GemClock(GEM 標準號),同一時刻但採 SEMI E5 16 字元格式'YYYYMMDDhhmmsscc'(與本機 S2F18 回覆同格式)；1027 維持 'yyyy/mm/dd hh:nn:ss'。
+〔20260805 韌體修正〕SVID 1027 的格式承諾 'yyyy/mm/dd hh:nn:ss' 未變，但其 '/' 與 ':' 先前是取自機台 Windows 地區設定的日期/時間分隔符，若現場把地區設定改成別的分隔符，1027 會靜默變成例如 '2026-08-04 15:49:53' 而與本表承諾不符。現已改為以字面字元組出，不再受地區設定影響，長度仍為 19。SVID 3 GemClock 與 S2F18 採無分隔符格式，本來就不受影響。</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2407,8 @@
 • PP_SIGNALTOWER：0=已套用，或空參數清單=解除覆寫(idempotent) / 1=參數本體不是 list、或某一 pair 不是 L[2] / 2=某一顏色值不在 0..2，或出現 RED / GREEN / YELLOW 以外的 CP 名稱。⚠ 回 1 或 2 時整包拒絕、完全不套用。
 • PP_MUSIC：0=已套用，或空參數清單=解除覆寫 / 1=參數本體不是 list、或某一 pair 不是 L[2] / 2=音效類別不在 1..4。⚠ 回 1 或 2 時整包拒絕、完全不套用；CP 名稱在本機被讀取但刻意不比對(貴端現場送的是零長度 &lt;A[0] ''&gt;)，故 CP 名稱不會造成拒絕。
 • ONLINE / ONLINE_REMOTE / ONLINE_LOCAL：0=控制狀態已變更 / 2=操作員已把機台設為 EQUIPMENT OFF-LINE，或組態 [SECS] AcceptHostOnlineRequest 為關閉(見我方補充 #4 的 20260805 追加項)。
-• ENERGY_SAVING：2=語法正確(含空參數清單 L[0])，認得命令但本機無節能子系統可執行 / 1=參數本體不是 list、任一 pair 不是 L[2]、CP 名稱不是 'STATE'、或 STATE 的值不在 0..1。</t>
+• ENERGY_SAVING：2=語法正確(含空參數清單 L[0])，認得命令但本機無節能子系統可執行 / 1=參數本體不是 list、任一 pair 不是 L[2]、CP 名稱不是 'STATE'、或 STATE 的值不在 0..1。
+〔20260805 追加：共用解析器修正的連帶影響〕上表的 HCACK 值域本身未變，但有一個**只在畸形封包下**才會出現的差異：LOTSTART / START_AGV / ENERGY_SAVING / PP_SIGNALTOWER / PP_MUSIC 這幾條命令在讀取 CP pair 時不檢查每一筆的讀取結果，先前若封包內夾了本機無法解讀的項目，解析會提早中斷而落到 HCACK=1；修正後解析會繼續走完整包，因而較可能落在「CP 名稱不認得」而回 HCACK=2。⚠ 兩者的實際結果相同 —— 命令一樣不執行、機台一樣不動作。格式正確的封包完全不受影響。本方尚未在實機上逐條實測此差異，故據實揭露。</t>
         </is>
       </c>
     </row>
@@ -22280,7 +22287,8 @@
 (1) 組成不同：本目錄(S5F6 / S5F8)的 ALTX 恆為「&lt;警報碼&gt; &lt;英文訊息&gt;」，固定取警報表的英文訊息欄，與介面語言無關；S5F1 事件的 ALTX 則是「&lt;警報碼&gt; &lt;該次發生時的訊息&gt;」，訊息取自當下介面語言(訊息為空時只送警報碼)。本機目前已登錄的 481 筆，中英訊息欄同為英文，故兩處文字目前一致；但未登錄的自由字串警報(見上一列第(2)類)本身就是介面語言的翻譯結果，中文介面時 ALTX 內含 Big5(CP950) 編碼的中文，且仍以 SECS-II &lt;A&gt; item 原樣送出(本機不做任何轉碼)。⚠ 貴端請以 CP950 或原始位元組(raw bytes)保存事件 ALTX，勿以 UTF-8 假設解碼，否則中文會毀損。
 (2) 馬達伺服警報是既有的例外：事件 ALTX 固定為「&lt;5xxxx&gt; Motor Error」，而本目錄同一筆是「&lt;5xxxx&gt; [M&lt;nn&gt; - &lt;軸別名&gt;] Motor --&lt;錯誤別&gt;」 —— 同一個 ALID、兩處文字不同。(汽缸 4xxxx、真空 6xxxx 等由警報表登錄的家族，事件訊息取自同一張表，故與本目錄該筆相同。)
 (3) 自由字串警報的 ALTX 形如「&lt;字串&gt; &lt;字串&gt;」：這一類的警報碼與訊息是同一字串，故同一句會重複一次(例：'Safety Door Open Safety Door Open')。若要顯示給操作員，建議先判斷「ALTX 正中央恰為一個空白、且前後兩半完全相同」，成立時只顯示前半。
-⚠ 總結：請一律以 ALID 對本目錄查表來識別警報，不要以 ALTX 字串比對做判斷、去重或觸發條件；事件 ALTX 僅供顯示與存證。</t>
+⚠ 總結：請一律以 ALID 對本目錄查表來識別警報，不要以 ALTX 字串比對做判斷、去重或觸發條件；事件 ALTX 僅供顯示與存證。
+〔20260805 追加項：第 (3) 類不在本目錄內的 S5F1〕非 AMR 模式(General.ini [HardwareInstall] UseAMR=0，即一般量產模式)下 Clean Out 排空完成時，機台會借用警報通道彈出一個操作員確認視窗，因此貴端會收到一筆ALID=3891410149 / ALTX="SnFKCleanOut SnFKCleanOut" 的 S5F1(發生時 ALCD=0x80，操作員關閉視窗後送解除 ALCD=0x00)。⚠ 這不是故障，而是「Clean Out 排空完成、請操作員確認」的提示;該號碼不在本目錄的 481 筆之內，請勿計入警報統計、也不要據以觸發停機處置。AMR 模式(UseAMR=1)下不會出現這一筆 —— 該分支改走全自動 Lot End。(本筆同時符合上一列第 (2) 類「自由字串警報」的形狀，故 ALTX 是同一句重複兩次。)</t>
         </is>
       </c>
     </row>
